--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_038.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_038.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="192">
   <si>
     <t>Sezione</t>
   </si>
@@ -365,16 +365,40 @@
     <t>Autorità mittente</t>
   </si>
   <si>
+    <t>Data formazione documento</t>
+  </si>
+  <si>
+    <t>evento.trascrizioneNascita.autoritaMittente</t>
+  </si>
+  <si>
+    <t>dataTrascrizione</t>
+  </si>
+  <si>
+    <t>evento.richiedente.idTipoRichiedente,!=,5</t>
+  </si>
+  <si>
+    <t>Estremi documento</t>
+  </si>
+  <si>
+    <t>estremiDocumento</t>
+  </si>
+  <si>
     <t>Nome ente</t>
   </si>
   <si>
-    <t>evento.trascrizioneNascita.autoritaMittente</t>
-  </si>
-  <si>
     <t>nomeEnte</t>
   </si>
   <si>
-    <t>evento.richiedente.idTipoRichiedente,!=,5</t>
+    <t>Stato ente</t>
+  </si>
+  <si>
+    <t>nazioneEnte</t>
+  </si>
+  <si>
+    <t>Stato ente - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeNazioneEnte</t>
   </si>
   <si>
     <t>Provincia ente</t>
@@ -401,16 +425,16 @@
     <t>nomeComuneEnte</t>
   </si>
   <si>
-    <t>Data formazione documento</t>
-  </si>
-  <si>
-    <t>dataTrascrizione</t>
-  </si>
-  <si>
-    <t>Estremi documento</t>
-  </si>
-  <si>
-    <t>estremiDocumento</t>
+    <t>Anagrafica Consolato</t>
+  </si>
+  <si>
+    <t>idAnagraficaConsolato</t>
+  </si>
+  <si>
+    <t>Anagrafica Consolato - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeAnagraficaConsolato</t>
   </si>
   <si>
     <t>Riassunto ente pubblico</t>
@@ -450,18 +474,6 @@
   </si>
   <si>
     <t>evento.trascrizioneNascita.attoEstero.enteEstero</t>
-  </si>
-  <si>
-    <t>Stato ente</t>
-  </si>
-  <si>
-    <t>nazioneEnte</t>
-  </si>
-  <si>
-    <t>Stato ente - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeNazioneEnte</t>
   </si>
   <si>
     <t>comuneEstero</t>
@@ -634,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.01171875" customWidth="true" bestFit="true"/>
@@ -3736,7 +3748,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>118</v>
@@ -3782,7 +3794,7 @@
         <v>127</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>118</v>
@@ -3805,7 +3817,7 @@
         <v>129</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>118</v>
@@ -3828,7 +3840,7 @@
         <v>131</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>118</v>
@@ -3845,19 +3857,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -3868,19 +3880,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
@@ -3891,163 +3903,163 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="C142" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149">
@@ -4055,22 +4067,22 @@
         <v>25</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150">
@@ -4078,22 +4090,22 @@
         <v>25</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="151">
@@ -4101,22 +4113,22 @@
         <v>25</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="152">
@@ -4124,7 +4136,7 @@
         <v>25</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>15</v>
@@ -4133,13 +4145,13 @@
         <v>27</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153">
@@ -4147,22 +4159,22 @@
         <v>25</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="154">
@@ -4170,7 +4182,7 @@
         <v>25</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>9</v>
@@ -4179,13 +4191,13 @@
         <v>27</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="155">
@@ -4193,22 +4205,22 @@
         <v>25</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="156">
@@ -4216,22 +4228,22 @@
         <v>25</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="157">
@@ -4239,22 +4251,22 @@
         <v>25</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="158">
@@ -4262,7 +4274,7 @@
         <v>25</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
@@ -4271,13 +4283,13 @@
         <v>27</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="159">
@@ -4285,7 +4297,7 @@
         <v>25</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>9</v>
@@ -4294,13 +4306,13 @@
         <v>27</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160">
@@ -4308,7 +4320,7 @@
         <v>25</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>9</v>
@@ -4317,13 +4329,13 @@
         <v>27</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="161">
@@ -4331,7 +4343,7 @@
         <v>25</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>9</v>
@@ -4340,13 +4352,13 @@
         <v>27</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="162">
@@ -4354,7 +4366,7 @@
         <v>25</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>9</v>
@@ -4363,13 +4375,13 @@
         <v>27</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163">
@@ -4377,7 +4389,7 @@
         <v>25</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>9</v>
@@ -4386,13 +4398,13 @@
         <v>27</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="164">
@@ -4400,7 +4412,7 @@
         <v>25</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>9</v>
@@ -4409,13 +4421,13 @@
         <v>27</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="165">
@@ -4423,7 +4435,7 @@
         <v>25</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>9</v>
@@ -4432,13 +4444,13 @@
         <v>27</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="166">
@@ -4446,7 +4458,7 @@
         <v>25</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>9</v>
@@ -4455,13 +4467,13 @@
         <v>27</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="167">
@@ -4469,7 +4481,7 @@
         <v>25</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>9</v>
@@ -4478,13 +4490,13 @@
         <v>27</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="168">
@@ -4492,7 +4504,7 @@
         <v>25</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>9</v>
@@ -4501,13 +4513,13 @@
         <v>27</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="169">
@@ -4515,7 +4527,7 @@
         <v>25</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>9</v>
@@ -4524,13 +4536,13 @@
         <v>27</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170">
@@ -4538,22 +4550,22 @@
         <v>25</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171">
@@ -4561,7 +4573,7 @@
         <v>25</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>9</v>
@@ -4570,13 +4582,13 @@
         <v>27</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172">
@@ -4584,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>9</v>
@@ -4593,13 +4605,13 @@
         <v>27</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="173">
@@ -4607,7 +4619,7 @@
         <v>25</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>9</v>
@@ -4616,13 +4628,13 @@
         <v>27</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174">
@@ -4630,22 +4642,22 @@
         <v>25</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="175">
@@ -4653,7 +4665,7 @@
         <v>25</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>9</v>
@@ -4662,13 +4674,13 @@
         <v>27</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
@@ -4676,7 +4688,7 @@
         <v>25</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>9</v>
@@ -4685,105 +4697,105 @@
         <v>27</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="181">
@@ -4791,22 +4803,22 @@
         <v>92</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="182">
@@ -4814,22 +4826,22 @@
         <v>92</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="183">
@@ -4837,22 +4849,22 @@
         <v>92</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="184">
@@ -4860,7 +4872,7 @@
         <v>92</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>15</v>
@@ -4869,13 +4881,13 @@
         <v>93</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="185">
@@ -4883,22 +4895,22 @@
         <v>92</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="186">
@@ -4906,7 +4918,7 @@
         <v>92</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>9</v>
@@ -4915,13 +4927,13 @@
         <v>93</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="187">
@@ -4929,22 +4941,22 @@
         <v>92</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="188">
@@ -4952,22 +4964,22 @@
         <v>92</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="189">
@@ -4975,22 +4987,22 @@
         <v>92</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="190">
@@ -4998,7 +5010,7 @@
         <v>92</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>9</v>
@@ -5007,13 +5019,13 @@
         <v>93</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="191">
@@ -5021,7 +5033,7 @@
         <v>92</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>9</v>
@@ -5030,13 +5042,13 @@
         <v>93</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="192">
@@ -5044,7 +5056,7 @@
         <v>92</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>9</v>
@@ -5053,13 +5065,13 @@
         <v>93</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="193">
@@ -5067,7 +5079,7 @@
         <v>92</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>9</v>
@@ -5076,13 +5088,13 @@
         <v>93</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="194">
@@ -5090,7 +5102,7 @@
         <v>92</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>9</v>
@@ -5099,13 +5111,13 @@
         <v>93</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="195">
@@ -5113,7 +5125,7 @@
         <v>92</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>9</v>
@@ -5122,13 +5134,13 @@
         <v>93</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="196">
@@ -5136,7 +5148,7 @@
         <v>92</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>9</v>
@@ -5145,13 +5157,13 @@
         <v>93</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="197">
@@ -5159,7 +5171,7 @@
         <v>92</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>9</v>
@@ -5168,13 +5180,13 @@
         <v>93</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="198">
@@ -5182,7 +5194,7 @@
         <v>92</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>9</v>
@@ -5191,13 +5203,13 @@
         <v>93</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="199">
@@ -5205,7 +5217,7 @@
         <v>92</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>9</v>
@@ -5214,13 +5226,13 @@
         <v>93</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="200">
@@ -5228,7 +5240,7 @@
         <v>92</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>9</v>
@@ -5237,13 +5249,13 @@
         <v>93</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="201">
@@ -5251,7 +5263,7 @@
         <v>92</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>9</v>
@@ -5260,13 +5272,13 @@
         <v>93</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="202">
@@ -5274,22 +5286,22 @@
         <v>92</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="203">
@@ -5297,7 +5309,7 @@
         <v>92</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>9</v>
@@ -5306,13 +5318,13 @@
         <v>93</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="204">
@@ -5320,7 +5332,7 @@
         <v>92</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>9</v>
@@ -5329,13 +5341,13 @@
         <v>93</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="205">
@@ -5343,7 +5355,7 @@
         <v>92</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>9</v>
@@ -5352,13 +5364,13 @@
         <v>93</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="206">
@@ -5366,22 +5378,22 @@
         <v>92</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="207">
@@ -5389,7 +5401,7 @@
         <v>92</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>9</v>
@@ -5398,13 +5410,13 @@
         <v>93</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="208">
@@ -5412,7 +5424,7 @@
         <v>92</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>9</v>
@@ -5421,122 +5433,122 @@
         <v>93</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>10</v>
@@ -5547,19 +5559,19 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>10</v>
@@ -5570,19 +5582,19 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>10</v>
@@ -5593,19 +5605,19 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="E216" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>10</v>
@@ -5616,19 +5628,19 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E217" s="2" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>10</v>
@@ -5639,19 +5651,19 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E218" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>10</v>
@@ -5662,19 +5674,19 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E219" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>10</v>
@@ -5685,19 +5697,19 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>10</v>
@@ -5708,19 +5720,19 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>10</v>
@@ -5731,19 +5743,19 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
@@ -5754,19 +5766,19 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>10</v>
@@ -5777,19 +5789,19 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>10</v>
@@ -5800,19 +5812,19 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>10</v>
@@ -5823,19 +5835,19 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>10</v>
@@ -5846,19 +5858,19 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
@@ -5869,19 +5881,19 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>10</v>
@@ -5892,410 +5904,410 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="C231" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D231" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D231" s="2" t="s">
+      <c r="E231" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E231" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="F231" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="F245" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>10</v>
@@ -6306,19 +6318,19 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>10</v>
@@ -6329,19 +6341,19 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>10</v>
@@ -6352,19 +6364,19 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>10</v>
@@ -6375,19 +6387,19 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>10</v>
@@ -6398,19 +6410,19 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>10</v>
@@ -6421,19 +6433,19 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>10</v>
@@ -6444,19 +6456,19 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>10</v>
@@ -6467,19 +6479,19 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>10</v>
@@ -6490,24 +6502,116 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E255" s="2" t="s">
+      <c r="B256" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F255" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G255" s="2" t="s">
+      <c r="E256" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G259" s="2" t="s">
         <v>18</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_038.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_038.xlsx
@@ -497,6 +497,9 @@
     <t>idAnsc</t>
   </si>
   <si>
+    <t>opzionale</t>
+  </si>
+  <si>
     <t>Provincia registrazione</t>
   </si>
   <si>
@@ -567,9 +570,6 @@
   </si>
   <si>
     <t>evento.trascrizioneNascita.eventoCollegato</t>
-  </si>
-  <si>
-    <t>opzionale</t>
   </si>
   <si>
     <t>Esito accertamento dichiarazione volontà</t>
@@ -5715,7 +5715,7 @@
         <v>10</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="221">
@@ -5723,7 +5723,7 @@
         <v>157</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>15</v>
@@ -5732,13 +5732,13 @@
         <v>159</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="222">
@@ -5746,7 +5746,7 @@
         <v>157</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>15</v>
@@ -5755,13 +5755,13 @@
         <v>159</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="223">
@@ -5769,7 +5769,7 @@
         <v>157</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>15</v>
@@ -5778,13 +5778,13 @@
         <v>159</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="224">
@@ -5792,7 +5792,7 @@
         <v>157</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>15</v>
@@ -5801,13 +5801,13 @@
         <v>159</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="225">
@@ -5815,7 +5815,7 @@
         <v>157</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>9</v>
@@ -5824,13 +5824,13 @@
         <v>159</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="226">
@@ -5838,7 +5838,7 @@
         <v>157</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>15</v>
@@ -5853,7 +5853,7 @@
         <v>10</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="227">
@@ -5861,7 +5861,7 @@
         <v>157</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>15</v>
@@ -5870,13 +5870,13 @@
         <v>159</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="228">
@@ -5884,7 +5884,7 @@
         <v>157</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>9</v>
@@ -5899,7 +5899,7 @@
         <v>10</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="229">
@@ -5907,7 +5907,7 @@
         <v>157</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>9</v>
@@ -5916,13 +5916,13 @@
         <v>159</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="230">
@@ -5930,7 +5930,7 @@
         <v>157</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>9</v>
@@ -5939,13 +5939,13 @@
         <v>159</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="231">
@@ -5953,7 +5953,7 @@
         <v>157</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>9</v>
@@ -5962,13 +5962,13 @@
         <v>159</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="232">
@@ -5976,7 +5976,7 @@
         <v>157</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>15</v>
@@ -5985,18 +5985,18 @@
         <v>159</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>158</v>
@@ -6005,7 +6005,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>160</v>
@@ -6014,136 +6014,136 @@
         <v>10</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>17</v>
@@ -6152,44 +6152,44 @@
         <v>10</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>20</v>
@@ -6198,99 +6198,99 @@
         <v>10</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F245" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="246">
@@ -6321,7 +6321,7 @@
         <v>186</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>15</v>
@@ -6330,7 +6330,7 @@
         <v>187</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>10</v>
@@ -6344,7 +6344,7 @@
         <v>186</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>15</v>
@@ -6353,7 +6353,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>10</v>
@@ -6367,7 +6367,7 @@
         <v>186</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>15</v>
@@ -6376,7 +6376,7 @@
         <v>187</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>10</v>
@@ -6390,7 +6390,7 @@
         <v>186</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>15</v>
@@ -6399,7 +6399,7 @@
         <v>187</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>10</v>
@@ -6413,7 +6413,7 @@
         <v>186</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>9</v>
@@ -6422,7 +6422,7 @@
         <v>187</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>186</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>15</v>
@@ -6459,7 +6459,7 @@
         <v>186</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>15</v>
@@ -6468,7 +6468,7 @@
         <v>187</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>10</v>
@@ -6482,7 +6482,7 @@
         <v>186</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>9</v>
@@ -6505,7 +6505,7 @@
         <v>186</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>9</v>
@@ -6514,7 +6514,7 @@
         <v>187</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>10</v>
@@ -6528,7 +6528,7 @@
         <v>186</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>9</v>
@@ -6537,7 +6537,7 @@
         <v>187</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>10</v>
@@ -6551,7 +6551,7 @@
         <v>186</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>9</v>
@@ -6560,7 +6560,7 @@
         <v>187</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>10</v>
@@ -6574,7 +6574,7 @@
         <v>186</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>187</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>10</v>
